--- a/data/file_generation/input/data_219/端侧订单记录.xlsx
+++ b/data/file_generation/input/data_219/端侧订单记录.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvchengguang\Documents\WXWork\1688854076421011\Cache\File\2026-02\lvcg\input\data_219\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenguanzhou/Downloads/标注0206-lvcg/澳鹏-数值统计数据编辑/input/data_219/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A76758E-60EB-474D-BDF1-854A9CDFFD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DE273F-1603-DE4A-914A-58DB35107B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="12月10日" sheetId="7" r:id="rId1"/>
@@ -1055,7 +1055,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1067,18 +1067,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1424,12 +1427,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="20.375" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1445,7 +1448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1461,7 +1464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1469,7 +1472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1477,7 +1480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -1493,7 +1496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1509,7 +1512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -1525,7 +1528,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -1533,7 +1536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1557,7 +1560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
@@ -1589,7 +1592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -1613,7 +1616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -1629,7 +1632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="4" t="s">
         <v>28</v>
       </c>
@@ -1637,7 +1640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -1645,7 +1648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
@@ -1653,7 +1656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1661,7 +1664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -1686,13 +1689,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="20.375" customWidth="1"/>
-    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>35</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
@@ -1724,7 +1727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1732,7 +1735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
@@ -1740,7 +1743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>40</v>
       </c>
@@ -1756,7 +1759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
@@ -1764,7 +1767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>42</v>
       </c>
@@ -1772,7 +1775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -1780,7 +1783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
@@ -1788,7 +1791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1796,7 +1799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1804,7 +1807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
@@ -1812,7 +1815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
@@ -1820,7 +1823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>49</v>
       </c>
@@ -1828,7 +1831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>50</v>
       </c>
@@ -1836,7 +1839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>51</v>
       </c>
@@ -1844,7 +1847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>52</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -1860,7 +1863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>54</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
         <v>55</v>
       </c>
@@ -1876,7 +1879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>56</v>
       </c>
@@ -1884,7 +1887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
         <v>57</v>
       </c>
@@ -1892,7 +1895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>58</v>
       </c>
@@ -1900,7 +1903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>59</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>60</v>
       </c>
@@ -1916,7 +1919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>61</v>
       </c>
@@ -1924,7 +1927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>62</v>
       </c>
@@ -1932,7 +1935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>63</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>64</v>
       </c>
@@ -1948,7 +1951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>65</v>
       </c>
@@ -1956,7 +1959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
         <v>67</v>
       </c>
@@ -1972,7 +1975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>68</v>
       </c>
@@ -1989,12 +1992,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="20.375" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2002,7 +2005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>71</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
@@ -2034,7 +2037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>73</v>
       </c>
@@ -2042,7 +2045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
         <v>74</v>
       </c>
@@ -2050,7 +2053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>75</v>
       </c>
@@ -2058,7 +2061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
@@ -2066,7 +2069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>77</v>
       </c>
@@ -2074,7 +2077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
         <v>78</v>
       </c>
@@ -2082,7 +2085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>79</v>
       </c>
@@ -2090,7 +2093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
         <v>80</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>81</v>
       </c>
@@ -2106,7 +2109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>82</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>83</v>
       </c>
@@ -2122,7 +2125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>84</v>
       </c>
@@ -2130,7 +2133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>85</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>86</v>
       </c>
@@ -2146,7 +2149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>87</v>
       </c>
@@ -2154,7 +2157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>88</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>89</v>
       </c>
@@ -2170,7 +2173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
@@ -2178,7 +2181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>91</v>
       </c>
@@ -2186,7 +2189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
         <v>92</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>93</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>94</v>
       </c>
@@ -2210,7 +2213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>95</v>
       </c>
@@ -2218,7 +2221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>96</v>
       </c>
@@ -2226,7 +2229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>97</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>98</v>
       </c>
@@ -2242,7 +2245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>99</v>
       </c>
@@ -2250,7 +2253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>100</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>101</v>
       </c>
@@ -2266,7 +2269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
         <v>102</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>103</v>
       </c>
@@ -2282,7 +2285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
         <v>104</v>
       </c>
@@ -2290,7 +2293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
         <v>105</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
         <v>106</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
         <v>107</v>
       </c>
@@ -2314,7 +2317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
         <v>108</v>
       </c>
@@ -2322,7 +2325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>109</v>
       </c>
@@ -2339,12 +2342,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B151"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="20.375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>110</v>
       </c>
@@ -2360,7 +2363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>111</v>
       </c>
@@ -2368,7 +2371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>112</v>
       </c>
@@ -2376,7 +2379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>113</v>
       </c>
@@ -2384,7 +2387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>114</v>
       </c>
@@ -2392,7 +2395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
         <v>115</v>
       </c>
@@ -2400,7 +2403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>116</v>
       </c>
@@ -2408,7 +2411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
         <v>117</v>
       </c>
@@ -2416,7 +2419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>118</v>
       </c>
@@ -2424,7 +2427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
@@ -2432,7 +2435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>120</v>
       </c>
@@ -2440,7 +2443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
         <v>121</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>122</v>
       </c>
@@ -2456,7 +2459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>123</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>124</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>125</v>
       </c>
@@ -2480,7 +2483,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -2488,7 +2491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>127</v>
       </c>
@@ -2496,7 +2499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>128</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>129</v>
       </c>
@@ -2512,7 +2515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>130</v>
       </c>
@@ -2520,7 +2523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
         <v>131</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>132</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
         <v>133</v>
       </c>
@@ -2544,7 +2547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>134</v>
       </c>
@@ -2552,7 +2555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>135</v>
       </c>
@@ -2560,7 +2563,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>136</v>
       </c>
@@ -2568,7 +2571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>137</v>
       </c>
@@ -2576,7 +2579,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>138</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>139</v>
       </c>
@@ -2592,7 +2595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>140</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>141</v>
       </c>
@@ -2608,7 +2611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>142</v>
       </c>
@@ -2616,7 +2619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
         <v>143</v>
       </c>
@@ -2624,7 +2627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>144</v>
       </c>
@@ -2632,7 +2635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
         <v>145</v>
       </c>
@@ -2640,7 +2643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
         <v>146</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
         <v>147</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
         <v>148</v>
       </c>
@@ -2664,7 +2667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
         <v>149</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>150</v>
       </c>
@@ -2680,7 +2683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
         <v>151</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>152</v>
       </c>
@@ -2696,7 +2699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
         <v>153</v>
       </c>
@@ -2704,7 +2707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
         <v>154</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
         <v>155</v>
       </c>
@@ -2720,7 +2723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
         <v>156</v>
       </c>
@@ -2728,7 +2731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
         <v>157</v>
       </c>
@@ -2736,7 +2739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
         <v>158</v>
       </c>
@@ -2744,7 +2747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
         <v>159</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
         <v>160</v>
       </c>
@@ -2760,7 +2763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="3" t="s">
         <v>161</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" s="3" t="s">
         <v>162</v>
       </c>
@@ -2776,7 +2779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" s="3" t="s">
         <v>163</v>
       </c>
@@ -2784,7 +2787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" s="3" t="s">
         <v>164</v>
       </c>
@@ -2792,7 +2795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57" s="3" t="s">
         <v>165</v>
       </c>
@@ -2800,7 +2803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
         <v>166</v>
       </c>
@@ -2808,7 +2811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
         <v>167</v>
       </c>
@@ -2816,7 +2819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" s="3" t="s">
         <v>168</v>
       </c>
@@ -2824,7 +2827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
         <v>169</v>
       </c>
@@ -2832,7 +2835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62" s="3" t="s">
         <v>170</v>
       </c>
@@ -2840,7 +2843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63" s="3" t="s">
         <v>171</v>
       </c>
@@ -2848,7 +2851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64" s="3" t="s">
         <v>172</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
         <v>173</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66" s="3" t="s">
         <v>174</v>
       </c>
@@ -2872,7 +2875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67" s="3" t="s">
         <v>175</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68" s="3" t="s">
         <v>176</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69" s="3" t="s">
         <v>177</v>
       </c>
@@ -2896,7 +2899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70" s="3" t="s">
         <v>178</v>
       </c>
@@ -2904,7 +2907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
         <v>179</v>
       </c>
@@ -2912,402 +2915,402 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76" s="3" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1">
       <c r="A81" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1">
       <c r="A82" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1">
       <c r="A83" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1">
       <c r="A84" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1">
       <c r="A85" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1">
       <c r="A86" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1">
       <c r="A87" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1">
       <c r="A88" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1">
       <c r="A89" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1">
       <c r="A90" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1">
       <c r="A91" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1">
       <c r="A92" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1">
       <c r="A93" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1">
       <c r="A94" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1">
       <c r="A95" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1">
       <c r="A96" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1">
       <c r="A97" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1">
       <c r="A98" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1">
       <c r="A99" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1">
       <c r="A100" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1">
       <c r="A101" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1">
       <c r="A102" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1">
       <c r="A103" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1">
       <c r="A104" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1">
       <c r="A105" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1">
       <c r="A106" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1">
       <c r="A107" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1">
       <c r="A108" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1">
       <c r="A109" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1">
       <c r="A110" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1">
       <c r="A111" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1">
       <c r="A112" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1">
       <c r="A113" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1">
       <c r="A114" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1">
       <c r="A115" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1">
       <c r="A116" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1">
       <c r="A117" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1">
       <c r="A118" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1">
       <c r="A119" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1">
       <c r="A120" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1">
       <c r="A121" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1">
       <c r="A122" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1">
       <c r="A123" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1">
       <c r="A124" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1">
       <c r="A125" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1">
       <c r="A126" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1">
       <c r="A127" s="3" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1">
       <c r="A128" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1">
       <c r="A129" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1">
       <c r="A130" s="3" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1">
       <c r="A131" s="3" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1">
       <c r="A132" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1">
       <c r="A133" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1">
       <c r="A134" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1">
       <c r="A135" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1">
       <c r="A136" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1">
       <c r="A137" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1">
       <c r="A138" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1">
       <c r="A139" s="3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1">
       <c r="A140" s="3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1">
       <c r="A141" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1">
       <c r="A142" s="3" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1">
       <c r="A143" s="3" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1">
       <c r="A144" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1">
       <c r="A145" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1">
       <c r="A146" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1">
       <c r="A147" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1">
       <c r="A148" s="3" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1">
       <c r="A149" s="3" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1">
       <c r="A150" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1">
       <c r="A151" s="3" t="s">
         <v>259</v>
       </c>
@@ -3321,12 +3324,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B78"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="20.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3334,7 +3337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>260</v>
       </c>
@@ -3342,7 +3345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>261</v>
       </c>
@@ -3350,7 +3353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>262</v>
       </c>
@@ -3358,7 +3361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>263</v>
       </c>
@@ -3366,7 +3369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>264</v>
       </c>
@@ -3374,7 +3377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
         <v>265</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>266</v>
       </c>
@@ -3390,7 +3393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
         <v>267</v>
       </c>
@@ -3398,7 +3401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
         <v>268</v>
       </c>
@@ -3406,7 +3409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
         <v>269</v>
       </c>
@@ -3414,7 +3417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>270</v>
       </c>
@@ -3422,7 +3425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
         <v>271</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>272</v>
       </c>
@@ -3438,7 +3441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>273</v>
       </c>
@@ -3446,7 +3449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>274</v>
       </c>
@@ -3454,7 +3457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>275</v>
       </c>
@@ -3462,7 +3465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>276</v>
       </c>
@@ -3470,7 +3473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>277</v>
       </c>
@@ -3478,7 +3481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>278</v>
       </c>
@@ -3486,7 +3489,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>279</v>
       </c>
@@ -3494,7 +3497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
         <v>280</v>
       </c>
@@ -3502,7 +3505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
         <v>281</v>
       </c>
@@ -3510,7 +3513,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>282</v>
       </c>
@@ -3518,7 +3521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
         <v>283</v>
       </c>
@@ -3526,7 +3529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="3" t="s">
         <v>284</v>
       </c>
@@ -3534,7 +3537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>285</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>286</v>
       </c>
@@ -3550,7 +3553,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>287</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" s="3" t="s">
         <v>288</v>
       </c>
@@ -3566,7 +3569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>289</v>
       </c>
@@ -3574,7 +3577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>290</v>
       </c>
@@ -3582,7 +3585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>291</v>
       </c>
@@ -3590,7 +3593,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>292</v>
       </c>
@@ -3598,7 +3601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
         <v>293</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="3" t="s">
         <v>294</v>
       </c>
@@ -3614,7 +3617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
         <v>295</v>
       </c>
@@ -3622,7 +3625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="3" t="s">
         <v>296</v>
       </c>
@@ -3630,7 +3633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
         <v>297</v>
       </c>
@@ -3638,7 +3641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
         <v>298</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
         <v>299</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>300</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
         <v>301</v>
       </c>
@@ -3670,7 +3673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="3" t="s">
         <v>302</v>
       </c>
@@ -3678,7 +3681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
         <v>303</v>
       </c>
@@ -3686,7 +3689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" s="3" t="s">
         <v>304</v>
       </c>
@@ -3694,7 +3697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
         <v>305</v>
       </c>
@@ -3702,7 +3705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
         <v>306</v>
       </c>
@@ -3710,7 +3713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
         <v>307</v>
       </c>
@@ -3718,7 +3721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
         <v>308</v>
       </c>
@@ -3726,7 +3729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
         <v>309</v>
       </c>
@@ -3734,7 +3737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
         <v>310</v>
       </c>
@@ -3742,7 +3745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="3" t="s">
         <v>311</v>
       </c>
@@ -3750,7 +3753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" s="3" t="s">
         <v>312</v>
       </c>
@@ -3758,7 +3761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" s="3" t="s">
         <v>313</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" s="3" t="s">
         <v>314</v>
       </c>
@@ -3774,7 +3777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57" s="3" t="s">
         <v>315</v>
       </c>
@@ -3782,7 +3785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" s="3" t="s">
         <v>316</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
         <v>317</v>
       </c>
@@ -3798,7 +3801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" s="3" t="s">
         <v>318</v>
       </c>
@@ -3806,7 +3809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
         <v>319</v>
       </c>
@@ -3814,7 +3817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62" s="3" t="s">
         <v>320</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63" s="3" t="s">
         <v>321</v>
       </c>
@@ -3830,7 +3833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64" s="3" t="s">
         <v>322</v>
       </c>
@@ -3838,7 +3841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
         <v>323</v>
       </c>
@@ -3846,7 +3849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66" s="3" t="s">
         <v>324</v>
       </c>
@@ -3854,7 +3857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67" s="3" t="s">
         <v>325</v>
       </c>
@@ -3862,7 +3865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68" s="3" t="s">
         <v>326</v>
       </c>
@@ -3870,7 +3873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69" s="3" t="s">
         <v>327</v>
       </c>
@@ -3878,7 +3881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70" s="3" t="s">
         <v>328</v>
       </c>
@@ -3886,7 +3889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
         <v>329</v>
       </c>
@@ -3894,7 +3897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72" s="3" t="s">
         <v>330</v>
       </c>
@@ -3902,7 +3905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73" s="3" t="s">
         <v>331</v>
       </c>
@@ -3910,7 +3913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74" s="3" t="s">
         <v>332</v>
       </c>
@@ -3918,7 +3921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75" s="3" t="s">
         <v>333</v>
       </c>
@@ -3926,7 +3929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76" s="3" t="s">
         <v>334</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77" s="3" t="s">
         <v>335</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78" s="3" t="s">
         <v>336</v>
       </c>
@@ -3962,13 +3965,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B64"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="16.125" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3976,252 +3979,252 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="15.75">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="15.75">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="15.75">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="15.75">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="15.75">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="15.75">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="15.75">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="15.75">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="15.75">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="15.75">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="15.75">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="15.75">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2" ht="15.75">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="15.75">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:2" ht="15.75">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:2" ht="15.75">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:2" ht="15.75">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:2" ht="15.75">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:2" ht="15.75">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:2" ht="15.75">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:2" ht="15.75">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:2" ht="15.75">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:2" ht="15.75">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:2" ht="15.75">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:2" ht="15.75">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:2" ht="15.75">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:2" ht="15.75">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:2" ht="15.75">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:2" ht="15.75">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:2" ht="15.75">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:2" ht="15.75">
       <c r="A34" s="1"/>
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:2" ht="15.75">
       <c r="A35" s="1"/>
       <c r="B35" s="2"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:2" ht="15.75">
       <c r="A36" s="1"/>
       <c r="B36" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:2" ht="15.75">
       <c r="A37" s="1"/>
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:2" ht="15.75">
       <c r="A38" s="1"/>
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:2" ht="15.75">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:2" ht="15.75">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:2" ht="15.75">
       <c r="A41" s="1"/>
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:2">
       <c r="A42" s="1"/>
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:2">
       <c r="A43" s="1"/>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:2">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:2">
       <c r="A45" s="1"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:2">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:2">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:2">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:2">
       <c r="A49" s="1"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:2">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:2">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:2">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:2">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:2">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:2">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:2">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:2">
       <c r="A57" s="1"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:2">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:2">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:2">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:2">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:2">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:2">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:2">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
     </row>
@@ -4390,18 +4393,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D102F6A7-B599-48B4-AD11-C8F462221C6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8AF9B0E-6D13-41EA-BA28-F88D1C547C6F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A18067B-AA7E-44BA-8504-9A5C40FFD69C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2A557DF-AAC8-4B5D-A646-659EA0622E60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCBD6A62-B0D7-4EF0-B681-375B968E8558}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8A7AAA-05B3-45A9-9F50-2831E78A7C36}"/>
 </file>